--- a/src/pages/test/any_data_test_transaction.xlsx
+++ b/src/pages/test/any_data_test_transaction.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE778BC4-725F-45CC-8DCE-080C225644F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB03E0D-B55A-4A84-A340-FF1E15F34E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="薪資底稿" sheetId="1" r:id="rId1"/>
@@ -893,15 +893,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>388620</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>283651</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>47431</xdr:colOff>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -925,8 +925,56 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5875020" y="632460"/>
+          <a:off x="3992880" y="60960"/>
           <a:ext cx="5930071" cy="1303020"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>162057</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B41E0748-E64A-F153-2071-0CA46981D4E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect t="3906"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3352800" y="30480"/>
+          <a:ext cx="6339840" cy="5465577"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9959,6 +10007,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BBAB1CD-87BA-4832-9EE4-1F9702131F99}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
@@ -10003,6 +10054,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
